--- a/PROYECTO3_requisitos.xlsx
+++ b/PROYECTO3_requisitos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unaledu-my.sharepoint.com/personal/mzueta_unal_edu_co/Documents/2025-02/Intro IA/Practica 3/practica_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_9F425ECB97D9AECF8A160B63BB9D05477634D4C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D00D6C7-AA43-4B35-853B-C8865F5BB2A8}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_9F425ECB97D9AECF8A160B63BB9D05477634D4C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97C268AB-EFD9-4EA5-BC33-1548C731A751}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>Categoría</t>
   </si>
@@ -161,6 +161,15 @@
   </si>
   <si>
     <t>Responsable</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>Agricultura</t>
+  </si>
+  <si>
+    <t>Notas</t>
   </si>
 </sst>
 </file>
@@ -200,7 +209,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -223,16 +232,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -248,6 +271,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,16 +564,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,8 +587,11 @@
       <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -570,9 +601,14 @@
       <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -583,7 +619,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -594,7 +630,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -605,7 +641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -616,7 +652,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -627,7 +663,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -638,7 +674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -649,7 +685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -660,7 +696,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -671,7 +707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -682,7 +718,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -693,7 +729,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -704,7 +740,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -715,7 +751,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>

--- a/PROYECTO3_requisitos.xlsx
+++ b/PROYECTO3_requisitos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unaledu-my.sharepoint.com/personal/mzueta_unal_edu_co/Documents/2025-02/Intro IA/Practica 3/practica_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_9F425ECB97D9AECF8A160B63BB9D05477634D4C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97C268AB-EFD9-4EA5-BC33-1548C731A751}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_9F425ECB97D9AECF8A160B63BB9D05477634D4C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BD74CD-26DA-486B-9018-FDE645F8A0BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -253,7 +253,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -568,10 +568,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
     <col min="3" max="3" width="71.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/PROYECTO3_requisitos.xlsx
+++ b/PROYECTO3_requisitos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unaledu-my.sharepoint.com/personal/mzueta_unal_edu_co/Documents/2025-02/Intro IA/Practica 3/practica_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_9F425ECB97D9AECF8A160B63BB9D05477634D4C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88BD74CD-26DA-486B-9018-FDE645F8A0BF}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_9F425ECB97D9AECF8A160B63BB9D05477634D4C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86DFE26D-6739-42DA-9E2A-B8F74F1B5FC1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>Categoría</t>
   </si>
@@ -166,10 +166,13 @@
     <t>Manuel</t>
   </si>
   <si>
-    <t>Agricultura</t>
-  </si>
-  <si>
     <t>Notas</t>
+  </si>
+  <si>
+    <t>Figuras</t>
+  </si>
+  <si>
+    <t>Ya los resultados estan, falta documentar</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
         <v>46</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -605,7 +608,7 @@
         <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -618,6 +621,9 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -628,6 +634,12 @@
       </c>
       <c r="C4" t="s">
         <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
